--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/07A_Kreditkonto_und_Saldenstaffel.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/07A_Kreditkonto_und_Saldenstaffel.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objektive_Geldfluesse" sheetId="1" r:id="R3c79d00d8e114de0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zinsstaffel_bis_3107" sheetId="2" r:id="R43daf86e95e74ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien_31_07_2025" sheetId="3" r:id="R07801654798a4c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlung_15_000" sheetId="4" r:id="Reb49bd4486a3484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien_04_03_2026" sheetId="5" r:id="R4510a11b576749d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="6" r:id="R454a79cca3dc4e04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objektive_Geldfluesse" sheetId="1" r:id="R7260cf81feb54106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zinsstaffel_bis_3107" sheetId="2" r:id="Rbf4eb96b02b44776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien_31_07_2025" sheetId="3" r:id="R95464e66e1674e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlung_15_000" sheetId="4" r:id="Rcabdb39cdb324aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szenarien_04_03_2026" sheetId="5" r:id="Re2e3eccae7494706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="6" r:id="R4088156ec32d48fc"/>
   </x:sheets>
 </x:workbook>
 </file>
